--- a/backend-code/f2025.xlsx
+++ b/backend-code/f2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fyp\Smart-Scheduler\backend-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44260E90-DBEA-4B4D-8B4C-9C9D703E38C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8465AED-2656-4E9E-BF10-D66D29465D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Faculty" sheetId="1" r:id="rId1"/>
@@ -1088,16 +1088,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G99"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3088,9 +3088,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>210</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>211</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>212</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>213</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>214</v>
       </c>
@@ -3275,9 +3275,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -3362,13 +3362,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="57.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>90</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>106</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -3596,16 +3596,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1300</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
